--- a/data/reports/2024-09-09/2024-09-09_duplicates.xlsx
+++ b/data/reports/2024-09-09/2024-09-09_duplicates.xlsx
@@ -145,7 +145,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004723</t>
+    <t>RMD0005813</t>
   </si>
   <si>
     <t>CoreTel Communications, Inc.</t>
@@ -161,28 +161,28 @@
     <t>Core Communications, Inc., Ton80 Communications, LLC, CoreTel Alabama, Inc., CoreTel Delaware, Inc., CoreTel Florida, Inc., CoreTel Georgia, Inc., CoreTel Kansas, Inc., CoreTel Kentucky, Inc., CoreTel Massachusetts, Inc., CoreTel New Jersey, Inc., CoreTel Virginia, Inc., CoreTel West Virginia, Inc., CoreTel Washington, Inc.,</t>
   </si>
   <si>
+    <t>Glenn Dalgliesh</t>
+  </si>
+  <si>
+    <t>VP of Operations</t>
+  </si>
+  <si>
+    <t>NOC</t>
+  </si>
+  <si>
+    <t>'+14439121000</t>
+  </si>
+  <si>
+    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004723</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005813</t>
-  </si>
-  <si>
-    <t>Glenn Dalgliesh</t>
-  </si>
-  <si>
-    <t>VP of Operations</t>
-  </si>
-  <si>
-    <t>NOC</t>
-  </si>
-  <si>
-    <t>'+14439121000</t>
-  </si>
-  <si>
-    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004139</t>
@@ -225,10 +225,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008972</t>
+  </si>
+  <si>
+    <t>Media Flint, Inc.</t>
+  </si>
+  <si>
+    <t>15260 Ventura Boulevard
+Suite 1200 PMB 492
+Sherman Oaks California 91403</t>
+  </si>
+  <si>
+    <t>U.S. Virgin Islands</t>
+  </si>
+  <si>
+    <t>AvidTrak</t>
+  </si>
+  <si>
+    <t>null
+null CA
+California</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008973</t>
-  </si>
-  <si>
-    <t>Media Flint, Inc.</t>
   </si>
   <si>
     <t>15260 Ventura Boulevard
@@ -236,32 +258,10 @@
 Sherman Oaks CA 91403</t>
   </si>
   <si>
-    <t>U.S. Virgin Islands</t>
-  </si>
-  <si>
-    <t>AvidTrak</t>
-  </si>
-  <si>
-    <t>null
-null CA
-California</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008972</t>
-  </si>
-  <si>
-    <t>15260 Ventura Boulevard
-Suite 1200 PMB 492
-Sherman Oaks California 91403</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -277,6 +277,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -286,25 +304,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009205</t>
+    <t>RMD0009084</t>
   </si>
   <si>
     <t>ADCOM Technologies, LLC</t>
@@ -318,6 +318,12 @@
     <t>ON DEMAND Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009205</t>
+  </si>
+  <si>
     <t>Dean Franks</t>
   </si>
   <si>
@@ -340,13 +346,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009084</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008869</t>
+    <t>RMD0006774</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -356,9 +356,18 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Sage Network &amp; Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008869</t>
+  </si>
+  <si>
     <t>Rick Minyard</t>
   </si>
   <si>
@@ -378,15 +387,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006774</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004389</t>
@@ -469,10 +469,20 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1f0635261b85f81002beea82f54bcbec&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0005785</t>
+  </si>
+  <si>
+    <t>Edge Fibernet</t>
+  </si>
+  <si>
+    <t>5004 4th Avenue
+Brooklyn New York 11220</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0005786</t>
-  </si>
-  <si>
-    <t>Edge Fibernet</t>
   </si>
   <si>
     <t>254 36th Street
@@ -483,16 +493,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005785</t>
-  </si>
-  <si>
-    <t>5004 4th Avenue
-Brooklyn New York 11220</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0007488</t>
   </si>
   <si>
@@ -596,7 +596,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=89cc84f51b4af01068d1a82eac4bcb3e&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004701</t>
+    <t>RMD0003052</t>
   </si>
   <si>
     <t>Jaintel LLC</t>
@@ -606,15 +606,33 @@
 DE 19806-3334 Wilmington, United States</t>
   </si>
   <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>Elayaraja Jinadoss</t>
   </si>
   <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>'+447341664829</t>
+  </si>
+  <si>
+    <t>2024-05-01</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004701</t>
+  </si>
+  <si>
     <t>Operations Director</t>
   </si>
   <si>
-    <t>Management</t>
-  </si>
-  <si>
     <t>'+1 737 237 0913</t>
   </si>
   <si>
@@ -622,24 +640,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b1f3904a1b4138107ccf20ecac4bcbbf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003052</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>'+447341664829</t>
-  </si>
-  <si>
-    <t>2024-05-01</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0003053</t>
@@ -670,7 +670,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003444</t>
+    <t>RMD0003442</t>
   </si>
   <si>
     <t>Shaw Telecom GP</t>
@@ -681,32 +681,6 @@
   </si>
   <si>
     <t>Canada</t>
-  </si>
-  <si>
-    <t>0031064868; 0031064884; 0031064900</t>
-  </si>
-  <si>
-    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
-  </si>
-  <si>
-    <t>Network Operations</t>
-  </si>
-  <si>
-    <t>TOPS-NR&amp;A</t>
-  </si>
-  <si>
-    <t>2728 Hopewell Place N.E.
-Calgary AE 17724
-Alberta</t>
-  </si>
-  <si>
-    <t>'+1-866-244-7475</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003442</t>
   </si>
   <si>
     <t>0031064868;
@@ -726,6 +700,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=322c4e941b8df0509294113d9c4bcb51&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003444</t>
+  </si>
+  <si>
+    <t>0031064868; 0031064884; 0031064900</t>
+  </si>
+  <si>
+    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
+  </si>
+  <si>
+    <t>Network Operations</t>
+  </si>
+  <si>
+    <t>TOPS-NR&amp;A</t>
+  </si>
+  <si>
+    <t>2728 Hopewell Place N.E.
+Calgary AE 17724
+Alberta</t>
+  </si>
+  <si>
+    <t>'+1-866-244-7475</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007384</t>
   </si>
   <si>
@@ -754,7 +754,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008577</t>
+    <t>RMD0005040</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -764,6 +764,12 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008577</t>
+  </si>
+  <si>
     <t>BatchDialer</t>
   </si>
   <si>
@@ -780,12 +786,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005040</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005569</t>
@@ -836,7 +836,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
+    <t>RMD0005297</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -849,6 +849,12 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007936</t>
+  </si>
+  <si>
     <t>Syed Omar Farooq Shah</t>
   </si>
   <si>
@@ -858,13 +864,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005585</t>
+    <t>RMD0005574</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -878,6 +878,22 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
+  </si>
+  <si>
+    <t>187 Plymouth Ave
+Fall River MA 02721</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005585</t>
+  </si>
+  <si>
     <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
   </si>
   <si>
@@ -891,23 +907,7 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005574</t>
-  </si>
-  <si>
-    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
-  </si>
-  <si>
-    <t>187 Plymouth Ave
-Fall River MA 02721</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007962</t>
@@ -993,7 +993,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007696</t>
+    <t>RMD0007716</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -1003,16 +1003,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007696</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007716</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -1022,6 +1022,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -1035,12 +1041,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008423</t>
@@ -1074,7 +1074,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1084,12 +1084,6 @@
 Greensboro NC 27401</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
     <t>null
 null NC</t>
   </si>
@@ -1097,6 +1091,12 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008451</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008611</t>
   </si>
   <si>
@@ -1116,25 +1116,25 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008612</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008610</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008759</t>
@@ -6286,16 +6286,28 @@
         <v>46</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="M5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R5" s="1" t="s">
         <v>26</v>
       </c>
@@ -6303,16 +6315,16 @@
         <v>26</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1">
         <v>17118795</v>
@@ -6336,28 +6348,16 @@
         <v>46</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
         <v>26</v>
       </c>
@@ -6365,7 +6365,7 @@
         <v>26</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
@@ -6634,9 +6634,11 @@
       <c r="O11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>30</v>
@@ -6647,14 +6649,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6681,7 +6685,7 @@
         <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>80</v>
@@ -6690,13 +6694,11 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>30</v>
@@ -6707,9 +6709,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>91</v>
       </c>
@@ -6728,55 +6728,41 @@
         <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q13" s="1"/>
       <c r="R13" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B14" s="1">
         <v>23003460</v>
@@ -6788,32 +6774,46 @@
         <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R14" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
@@ -6839,54 +6839,40 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>23250467</v>
@@ -6903,33 +6889,47 @@
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
         <v>118</v>
       </c>
@@ -7095,13 +7095,13 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>127</v>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>26</v>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>26</v>
@@ -7580,55 +7580,61 @@
         <v>184</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+        <v>185</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="J29" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
         <v>39</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="1">
         <v>30758643</v>
@@ -7640,34 +7646,28 @@
         <v>184</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>193</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>192</v>
+        <v>27</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>194</v>
@@ -7677,10 +7677,10 @@
         <v>39</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>26</v>
@@ -7709,7 +7709,7 @@
         <v>30</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -7755,7 +7755,7 @@
         <v>30</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -7773,14 +7773,14 @@
         <v>199</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>204</v>
       </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>30</v>
@@ -7822,45 +7822,33 @@
       <c r="I33" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>213</v>
-      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>215</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1">
         <v>31064850</v>
@@ -7878,30 +7866,42 @@
         <v>209</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="Q34" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R34" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U34" s="1"/>
       <c r="V34" s="1" t="s">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>30</v>
@@ -8033,48 +8033,34 @@
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>236</v>
-      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>237</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
       <c r="P37" s="1"/>
-      <c r="Q37" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q37" s="1"/>
       <c r="R37" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B38" s="1">
         <v>31124688</v>
@@ -8093,25 +8079,39 @@
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>238</v>
+      </c>
       <c r="M38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
+        <v>232</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
+      <c r="Q38" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R38" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>26</v>
@@ -8262,45 +8262,33 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>203</v>
-      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
       <c r="M41" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>261</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
       <c r="P41" s="1"/>
-      <c r="Q41" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q41" s="1"/>
       <c r="R41" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B42" s="1">
         <v>31294614</v>
@@ -8320,24 +8308,36 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="J42" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="M42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
+        <v>258</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
+      <c r="Q42" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R42" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
@@ -8369,48 +8369,42 @@
       <c r="H43" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
+      <c r="I43" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L43" s="1" t="s">
+      <c r="N43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="1" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B44" s="1">
         <v>31356652</v>
@@ -8431,14 +8425,18 @@
         <v>268</v>
       </c>
       <c r="H44" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
         <v>277</v>
       </c>
@@ -8446,22 +8444,24 @@
         <v>27</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="1" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U44" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V44" s="1" t="s">
         <v>278</v>
       </c>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>30</v>
@@ -8787,9 +8787,15 @@
       <c r="F51" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="G51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -8833,15 +8839,9 @@
       <c r="F52" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -8880,55 +8880,41 @@
         <v>313</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B54" s="1">
         <v>31445216</v>
@@ -8940,32 +8926,46 @@
         <v>313</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="M54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
+        <v>313</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="R54" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -9100,7 +9100,7 @@
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
-        <v>29</v>
+        <v>333</v>
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
@@ -9117,12 +9117,12 @@
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B58" s="1">
         <v>31457815</v>
@@ -9146,7 +9146,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>335</v>
+        <v>29</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -9231,38 +9231,50 @@
         <v>30</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
+      <c r="J60" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="M60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
+        <v>339</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
+      <c r="Q60" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R60" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B61" s="1">
         <v>31475270</v>
@@ -9277,41 +9289,29 @@
         <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>348</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
       <c r="P61" s="1"/>
-      <c r="Q61" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q61" s="1"/>
       <c r="R61" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
@@ -9358,7 +9358,7 @@
         <v>354</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R62" s="1" t="s">
         <v>30</v>
@@ -9464,7 +9464,7 @@
         <v>366</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R64" s="1" t="s">
         <v>30</v>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>30</v>
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P73" s="1"/>
       <c r="Q73" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>30</v>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="P76" s="1"/>
       <c r="Q76" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R76" s="1" t="s">
         <v>30</v>
@@ -10179,7 +10179,7 @@
         <v>30</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
@@ -10248,7 +10248,7 @@
         <v>436</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R79" s="1" t="s">
         <v>26</v>
@@ -10286,7 +10286,7 @@
         <v>440</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>441</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="P80" s="1"/>
       <c r="Q80" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R80" s="1" t="s">
         <v>30</v>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="P81" s="1"/>
       <c r="Q81" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R81" s="1" t="s">
         <v>30</v>
@@ -10515,7 +10515,7 @@
         <v>245</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>461</v>
@@ -10528,7 +10528,7 @@
       </c>
       <c r="P84" s="1"/>
       <c r="Q84" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R84" s="1" t="s">
         <v>30</v>
@@ -10754,7 +10754,7 @@
         <v>490</v>
       </c>
       <c r="Q88" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R88" s="1" t="s">
         <v>26</v>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="P90" s="1"/>
       <c r="Q90" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R90" s="1" t="s">
         <v>30</v>
@@ -10946,13 +10946,13 @@
         <v>27</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>511</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J92" s="1" t="s">
         <v>512</v>
@@ -10961,7 +10961,7 @@
         <v>513</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M92" s="1" t="s">
         <v>510</v>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="P94" s="1"/>
       <c r="Q94" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R94" s="1" t="s">
         <v>30</v>
@@ -11123,7 +11123,7 @@
         <v>533</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M95" s="1" t="s">
         <v>530</v>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="P96" s="1"/>
       <c r="Q96" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R96" s="1" t="s">
         <v>30</v>
@@ -11425,7 +11425,7 @@
         <v>30</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>28</v>
@@ -11471,7 +11471,7 @@
         <v>30</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="P103" s="1"/>
       <c r="Q103" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R103" s="1" t="s">
         <v>30</v>
@@ -11578,13 +11578,13 @@
         <v>27</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J104" s="1" t="s">
         <v>573</v>
@@ -11593,7 +11593,7 @@
         <v>59</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M104" s="1" t="s">
         <v>572</v>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="P104" s="1"/>
       <c r="Q104" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R104" s="1" t="s">
         <v>30</v>
@@ -11668,7 +11668,7 @@
       </c>
       <c r="P105" s="1"/>
       <c r="Q105" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R105" s="1" t="s">
         <v>26</v>
@@ -12196,13 +12196,13 @@
         <v>27</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J115" s="1" t="s">
         <v>638</v>
@@ -12284,7 +12284,7 @@
       </c>
       <c r="P116" s="1"/>
       <c r="Q116" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R116" s="1" t="s">
         <v>26</v>
@@ -12333,7 +12333,7 @@
         <v>656</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>651</v>
@@ -12389,7 +12389,7 @@
         <v>59</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M118" s="1" t="s">
         <v>660</v>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="P124" s="1"/>
       <c r="Q124" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R124" s="1" t="s">
         <v>30</v>
@@ -12896,10 +12896,10 @@
         <v>719</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M127" s="1" t="s">
         <v>718</v>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="P127" s="1"/>
       <c r="Q127" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R127" s="1" t="s">
         <v>30</v>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="P129" s="1"/>
       <c r="Q129" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R129" s="1" t="s">
         <v>30</v>
@@ -13121,7 +13121,7 @@
         <v>30</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>28</v>
@@ -13145,7 +13145,7 @@
         <v>742</v>
       </c>
       <c r="N131" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O131" s="1" t="s">
         <v>745</v>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="P132" s="1"/>
       <c r="Q132" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R132" s="1" t="s">
         <v>30</v>
@@ -13253,7 +13253,7 @@
         <v>756</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M133" s="1" t="s">
         <v>754</v>
@@ -13311,7 +13311,7 @@
         <v>245</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M134" s="1" t="s">
         <v>760</v>
@@ -13367,7 +13367,7 @@
         <v>769</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M135" s="1" t="s">
         <v>766</v>
@@ -13438,7 +13438,7 @@
       </c>
       <c r="P136" s="1"/>
       <c r="Q136" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R136" s="1" t="s">
         <v>30</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="P138" s="1"/>
       <c r="Q138" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R138" s="1" t="s">
         <v>30</v>
@@ -13679,7 +13679,7 @@
         <v>30</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G141" s="1"/>
       <c r="H141" s="1"/>
@@ -13697,14 +13697,14 @@
         <v>804</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O141" s="1" t="s">
         <v>805</v>
       </c>
       <c r="P141" s="1"/>
       <c r="Q141" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R141" s="1" t="s">
         <v>30</v>
@@ -13985,7 +13985,7 @@
         <v>837</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M146" s="1" t="s">
         <v>838</v>
@@ -14060,7 +14060,7 @@
       </c>
       <c r="P147" s="1"/>
       <c r="Q147" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R147" s="1" t="s">
         <v>30</v>
@@ -14089,7 +14089,7 @@
         <v>30</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>848</v>
@@ -14162,7 +14162,7 @@
       </c>
       <c r="P149" s="1"/>
       <c r="Q149" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R149" s="1" t="s">
         <v>30</v>
@@ -14216,7 +14216,7 @@
       </c>
       <c r="P150" s="1"/>
       <c r="Q150" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R150" s="1" t="s">
         <v>30</v>
@@ -14380,7 +14380,7 @@
         <v>882</v>
       </c>
       <c r="Q153" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R153" s="1" t="s">
         <v>26</v>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="P157" s="1"/>
       <c r="Q157" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R157" s="1" t="s">
         <v>30</v>
@@ -14617,7 +14617,7 @@
         <v>904</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M158" s="1"/>
       <c r="N158" s="1" t="s">
@@ -14670,7 +14670,7 @@
         <v>910</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L159" s="1" t="s">
         <v>911</v>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="P161" s="1"/>
       <c r="Q161" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R161" s="1" t="s">
         <v>26</v>
@@ -14823,7 +14823,7 @@
         <v>59</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M162" s="1"/>
       <c r="N162" s="1" t="s">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="P162" s="1"/>
       <c r="Q162" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R162" s="1" t="s">
         <v>30</v>
@@ -14907,7 +14907,7 @@
         <v>30</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G164" s="1"/>
       <c r="H164" s="1"/>
@@ -14916,21 +14916,21 @@
         <v>934</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L164" s="1" t="s">
         <v>203</v>
       </c>
       <c r="M164" s="1"/>
       <c r="N164" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O164" s="1" t="s">
         <v>935</v>
       </c>
       <c r="P164" s="1"/>
       <c r="Q164" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R164" s="1" t="s">
         <v>30</v>
@@ -15042,7 +15042,7 @@
       </c>
       <c r="P166" s="1"/>
       <c r="Q166" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R166" s="1" t="s">
         <v>30</v>
@@ -15102,7 +15102,7 @@
       </c>
       <c r="P167" s="1"/>
       <c r="Q167" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R167" s="1" t="s">
         <v>30</v>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="P168" s="1"/>
       <c r="Q168" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R168" s="1" t="s">
         <v>30</v>
@@ -15247,7 +15247,7 @@
         <v>30</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
@@ -15259,11 +15259,11 @@
         <v>59</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M170" s="1"/>
       <c r="N170" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O170" s="1" t="s">
         <v>971</v>
@@ -15304,7 +15304,7 @@
         <v>27</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>975</v>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="P171" s="1"/>
       <c r="Q171" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R171" s="1" t="s">
         <v>30</v>
@@ -15363,7 +15363,7 @@
         <v>30</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>28</v>
@@ -15387,14 +15387,14 @@
         <v>984</v>
       </c>
       <c r="N172" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O172" s="1" t="s">
         <v>985</v>
       </c>
       <c r="P172" s="1"/>
       <c r="Q172" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R172" s="1" t="s">
         <v>30</v>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="P173" s="1"/>
       <c r="Q173" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R173" s="1" t="s">
         <v>26</v>
@@ -15486,7 +15486,7 @@
         <v>27</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H174" s="1"/>
       <c r="I174" s="1"/>
@@ -15589,7 +15589,7 @@
         <v>1004</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M176" s="1"/>
       <c r="N176" s="1" t="s">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="P179" s="1"/>
       <c r="Q179" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R179" s="1" t="s">
         <v>26</v>
@@ -15785,7 +15785,7 @@
         <v>30</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
@@ -15794,21 +15794,21 @@
         <v>1021</v>
       </c>
       <c r="K180" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L180" s="1" t="s">
         <v>1022</v>
       </c>
       <c r="M180" s="1"/>
       <c r="N180" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O180" s="1" t="s">
         <v>1023</v>
       </c>
       <c r="P180" s="1"/>
       <c r="Q180" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R180" s="1" t="s">
         <v>30</v>
@@ -15862,7 +15862,7 @@
       </c>
       <c r="P181" s="1"/>
       <c r="Q181" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R181" s="1" t="s">
         <v>30</v>
@@ -15969,7 +15969,7 @@
         <v>1043</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M183" s="1" t="s">
         <v>1044</v>
@@ -15982,7 +15982,7 @@
       </c>
       <c r="P183" s="1"/>
       <c r="Q183" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R183" s="1" t="s">
         <v>30</v>
@@ -16136,13 +16136,13 @@
         <v>27</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H186" s="1" t="s">
         <v>1065</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J186" s="1"/>
       <c r="K186" s="1"/>
@@ -16326,7 +16326,7 @@
       </c>
       <c r="P189" s="1"/>
       <c r="Q189" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R189" s="1" t="s">
         <v>30</v>
@@ -16429,7 +16429,7 @@
         <v>293</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M191" s="1" t="s">
         <v>1093</v>
@@ -16527,7 +16527,7 @@
         <v>30</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G193" s="1"/>
       <c r="H193" s="1"/>
@@ -16545,14 +16545,14 @@
         <v>1104</v>
       </c>
       <c r="N193" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O193" s="1" t="s">
         <v>1105</v>
       </c>
       <c r="P193" s="1"/>
       <c r="Q193" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R193" s="1" t="s">
         <v>30</v>
@@ -16608,7 +16608,7 @@
       </c>
       <c r="P194" s="1"/>
       <c r="Q194" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R194" s="1" t="s">
         <v>30</v>
@@ -16709,7 +16709,7 @@
         <v>59</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M196" s="1" t="s">
         <v>1123</v>
@@ -16722,7 +16722,7 @@
       </c>
       <c r="P196" s="1"/>
       <c r="Q196" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R196" s="1" t="s">
         <v>30</v>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="P197" s="1"/>
       <c r="Q197" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R197" s="1" t="s">
         <v>30</v>
@@ -16879,7 +16879,7 @@
         <v>30</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G199" s="1"/>
       <c r="H199" s="1"/>
@@ -16891,18 +16891,18 @@
         <v>470</v>
       </c>
       <c r="L199" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M199" s="1"/>
       <c r="N199" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O199" s="1" t="s">
         <v>1146</v>
       </c>
       <c r="P199" s="1"/>
       <c r="Q199" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R199" s="1" t="s">
         <v>30</v>
@@ -16951,7 +16951,7 @@
         <v>165</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M200" s="1" t="s">
         <v>1154</v>
@@ -16964,7 +16964,7 @@
       </c>
       <c r="P200" s="1"/>
       <c r="Q200" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R200" s="1" t="s">
         <v>30</v>
@@ -17120,7 +17120,7 @@
       </c>
       <c r="P203" s="1"/>
       <c r="Q203" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R203" s="1" t="s">
         <v>26</v>
@@ -17270,13 +17270,13 @@
         <v>27</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H206" s="1" t="s">
         <v>1186</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J206" s="1"/>
       <c r="K206" s="1"/>
@@ -17330,7 +17330,7 @@
         <v>1192</v>
       </c>
       <c r="K207" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L207" s="1" t="s">
         <v>1193</v>
@@ -17470,7 +17470,7 @@
       </c>
       <c r="P209" s="1"/>
       <c r="Q209" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R209" s="1" t="s">
         <v>30</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="P210" s="1"/>
       <c r="Q210" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R210" s="1" t="s">
         <v>30</v>
@@ -17580,7 +17580,7 @@
         <v>1229</v>
       </c>
       <c r="K211" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L211" s="1" t="s">
         <v>1230</v>
@@ -17596,7 +17596,7 @@
       </c>
       <c r="P211" s="1"/>
       <c r="Q211" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R211" s="1" t="s">
         <v>30</v>
@@ -17646,7 +17646,7 @@
         <v>1229</v>
       </c>
       <c r="K212" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L212" s="1" t="s">
         <v>1230</v>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="P212" s="1"/>
       <c r="Q212" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R212" s="1" t="s">
         <v>30</v>
@@ -17697,16 +17697,16 @@
         <v>30</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J213" s="1" t="s">
         <v>1244</v>
@@ -17721,7 +17721,7 @@
         <v>1243</v>
       </c>
       <c r="N213" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O213" s="1" t="s">
         <v>1246</v>
@@ -17763,7 +17763,7 @@
         <v>30</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>1249</v>
@@ -17783,7 +17783,7 @@
         <v>1243</v>
       </c>
       <c r="N214" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O214" s="1" t="s">
         <v>1246</v>
@@ -17898,10 +17898,10 @@
         <v>1263</v>
       </c>
       <c r="K216" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L216" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M216" s="1" t="s">
         <v>1264</v>
@@ -17976,7 +17976,7 @@
       </c>
       <c r="P217" s="1"/>
       <c r="Q217" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R217" s="1" t="s">
         <v>30</v>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="P218" s="1"/>
       <c r="Q218" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R218" s="1" t="s">
         <v>30</v>
@@ -18072,7 +18072,7 @@
         <v>1190</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H219" s="1"/>
       <c r="I219" s="1"/>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="P219" s="1"/>
       <c r="Q219" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R219" s="1" t="s">
         <v>30</v>
@@ -18186,7 +18186,7 @@
         <v>1288</v>
       </c>
       <c r="K221" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L221" s="1" t="s">
         <v>203</v>
@@ -18315,7 +18315,7 @@
         <v>1301</v>
       </c>
       <c r="L223" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M223" s="1" t="s">
         <v>1302</v>
@@ -18375,7 +18375,7 @@
         <v>1309</v>
       </c>
       <c r="L224" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M224" s="1" t="s">
         <v>1310</v>
@@ -18388,7 +18388,7 @@
       </c>
       <c r="P224" s="1"/>
       <c r="Q224" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R224" s="1" t="s">
         <v>30</v>
@@ -18446,7 +18446,7 @@
       </c>
       <c r="P225" s="1"/>
       <c r="Q225" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R225" s="1" t="s">
         <v>26</v>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="P226" s="1"/>
       <c r="Q226" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R226" s="1" t="s">
         <v>26</v>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="P227" s="1"/>
       <c r="Q227" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R227" s="1" t="s">
         <v>30</v>
@@ -18630,7 +18630,7 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R228" s="1" t="s">
         <v>30</v>
@@ -18694,7 +18694,7 @@
       </c>
       <c r="P229" s="1"/>
       <c r="Q229" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R229" s="1" t="s">
         <v>30</v>
@@ -18876,7 +18876,7 @@
       </c>
       <c r="P232" s="1"/>
       <c r="Q232" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R232" s="1" t="s">
         <v>30</v>
@@ -18927,7 +18927,7 @@
         <v>165</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M233" s="1" t="s">
         <v>1374</v>
@@ -18940,7 +18940,7 @@
       </c>
       <c r="P233" s="1"/>
       <c r="Q233" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R233" s="1" t="s">
         <v>30</v>
@@ -18978,13 +18978,13 @@
         <v>27</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H234" s="1" t="s">
         <v>1379</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J234" s="1" t="s">
         <v>1380</v>
@@ -19006,7 +19006,7 @@
       </c>
       <c r="P234" s="1"/>
       <c r="Q234" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R234" s="1" t="s">
         <v>30</v>
@@ -19125,7 +19125,7 @@
         <v>769</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M236" s="1" t="s">
         <v>1397</v>
@@ -19138,7 +19138,7 @@
       </c>
       <c r="P236" s="1"/>
       <c r="Q236" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R236" s="1" t="s">
         <v>30</v>
@@ -19204,7 +19204,7 @@
       </c>
       <c r="P237" s="1"/>
       <c r="Q237" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R237" s="1" t="s">
         <v>30</v>
@@ -19252,7 +19252,7 @@
         <v>1413</v>
       </c>
       <c r="K238" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L238" s="1" t="s">
         <v>1414</v>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="P238" s="1"/>
       <c r="Q238" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R238" s="1" t="s">
         <v>30</v>
@@ -19332,7 +19332,7 @@
       </c>
       <c r="P239" s="1"/>
       <c r="Q239" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R239" s="1" t="s">
         <v>30</v>
@@ -19390,7 +19390,7 @@
       </c>
       <c r="P240" s="1"/>
       <c r="Q240" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R240" s="1" t="s">
         <v>30</v>
@@ -19638,7 +19638,7 @@
       </c>
       <c r="P244" s="1"/>
       <c r="Q244" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R244" s="1" t="s">
         <v>30</v>
@@ -19753,7 +19753,7 @@
         <v>1464</v>
       </c>
       <c r="L246" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M246" s="1" t="s">
         <v>1469</v>
@@ -19826,7 +19826,7 @@
       </c>
       <c r="P247" s="1"/>
       <c r="Q247" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R247" s="1" t="s">
         <v>26</v>
@@ -19870,10 +19870,10 @@
         <v>1480</v>
       </c>
       <c r="K248" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M248" s="1" t="s">
         <v>1479</v>
@@ -19886,7 +19886,7 @@
       </c>
       <c r="P248" s="1"/>
       <c r="Q248" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R248" s="1" t="s">
         <v>30</v>
@@ -19982,13 +19982,13 @@
         <v>27</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I250" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J250" s="1" t="s">
         <v>1486</v>
@@ -20136,7 +20136,7 @@
         <v>1509</v>
       </c>
       <c r="Q252" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R252" s="1" t="s">
         <v>30</v>
@@ -20185,7 +20185,7 @@
         <v>293</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M253" s="1" t="s">
         <v>1513</v>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="P253" s="1"/>
       <c r="Q253" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R253" s="1" t="s">
         <v>30</v>
@@ -20247,7 +20247,7 @@
         <v>293</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M254" s="1" t="s">
         <v>1513</v>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="P254" s="1"/>
       <c r="Q254" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R254" s="1" t="s">
         <v>30</v>
@@ -20380,7 +20380,7 @@
       </c>
       <c r="P256" s="1"/>
       <c r="Q256" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R256" s="1" t="s">
         <v>30</v>
@@ -20789,7 +20789,7 @@
         <v>1579</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M263" s="1" t="s">
         <v>1580</v>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="P263" s="1"/>
       <c r="Q263" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R263" s="1" t="s">
         <v>30</v>
@@ -20853,7 +20853,7 @@
         <v>1579</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M264" s="1" t="s">
         <v>1585</v>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="P264" s="1"/>
       <c r="Q264" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R264" s="1" t="s">
         <v>30</v>
@@ -20913,7 +20913,7 @@
         <v>581</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M265" s="1" t="s">
         <v>1594</v>
@@ -20926,7 +20926,7 @@
       </c>
       <c r="P265" s="1"/>
       <c r="Q265" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R265" s="1" t="s">
         <v>30</v>
@@ -21026,13 +21026,13 @@
         <v>27</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H267" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J267" s="1" t="s">
         <v>1607</v>
@@ -21054,7 +21054,7 @@
       </c>
       <c r="P267" s="1"/>
       <c r="Q267" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R267" s="1" t="s">
         <v>30</v>
@@ -21101,7 +21101,7 @@
         <v>293</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M268" s="1" t="s">
         <v>1615</v>
@@ -21165,7 +21165,7 @@
         <v>1624</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M269" s="1" t="s">
         <v>1625</v>
@@ -21178,7 +21178,7 @@
       </c>
       <c r="P269" s="1"/>
       <c r="Q269" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R269" s="1" t="s">
         <v>30</v>
@@ -21238,7 +21238,7 @@
       </c>
       <c r="P270" s="1"/>
       <c r="Q270" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R270" s="1" t="s">
         <v>30</v>
@@ -21287,7 +21287,7 @@
         <v>769</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M271" s="1" t="s">
         <v>1638</v>
@@ -21349,7 +21349,7 @@
         <v>769</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M272" s="1" t="s">
         <v>1638</v>
@@ -21415,7 +21415,7 @@
         <v>59</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M273" s="1" t="s">
         <v>1650</v>
@@ -21479,7 +21479,7 @@
         <v>59</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M274" s="1" t="s">
         <v>1659</v>
@@ -21528,13 +21528,13 @@
         <v>209</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H275" s="1" t="s">
         <v>1666</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J275" s="1" t="s">
         <v>1667</v>
@@ -21558,7 +21558,7 @@
         <v>1670</v>
       </c>
       <c r="Q275" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R275" s="1" t="s">
         <v>30</v>
@@ -21594,13 +21594,13 @@
         <v>209</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H276" s="1" t="s">
         <v>1666</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J276" s="1" t="s">
         <v>1667</v>
@@ -21624,7 +21624,7 @@
         <v>1670</v>
       </c>
       <c r="Q276" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R276" s="1" t="s">
         <v>30</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="P277" s="1"/>
       <c r="Q277" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R277" s="1" t="s">
         <v>30</v>
@@ -21750,7 +21750,7 @@
       </c>
       <c r="P278" s="1"/>
       <c r="Q278" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R278" s="1" t="s">
         <v>30</v>
@@ -21814,7 +21814,7 @@
       </c>
       <c r="P279" s="1"/>
       <c r="Q279" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R279" s="1" t="s">
         <v>30</v>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="P280" s="1"/>
       <c r="Q280" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R280" s="1" t="s">
         <v>30</v>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="P282" s="1"/>
       <c r="Q282" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R282" s="1" t="s">
         <v>30</v>
@@ -22056,7 +22056,7 @@
       </c>
       <c r="P283" s="1"/>
       <c r="Q283" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R283" s="1" t="s">
         <v>30</v>
@@ -22296,7 +22296,7 @@
         <v>1752</v>
       </c>
       <c r="Q287" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R287" s="1" t="s">
         <v>30</v>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="P288" s="1"/>
       <c r="Q288" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R288" s="1" t="s">
         <v>30</v>
@@ -22393,7 +22393,7 @@
         <v>30</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>1767</v>
@@ -22407,20 +22407,20 @@
         <v>1769</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M289" s="1" t="s">
         <v>1766</v>
       </c>
       <c r="N289" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O289" s="1" t="s">
         <v>1770</v>
       </c>
       <c r="P289" s="1"/>
       <c r="Q289" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R289" s="1" t="s">
         <v>30</v>
@@ -22453,7 +22453,7 @@
         <v>30</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G290" s="1"/>
       <c r="H290" s="1"/>
@@ -22465,20 +22465,20 @@
         <v>1774</v>
       </c>
       <c r="L290" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M290" s="1" t="s">
         <v>1766</v>
       </c>
       <c r="N290" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O290" s="1" t="s">
         <v>1775</v>
       </c>
       <c r="P290" s="1"/>
       <c r="Q290" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R290" s="1" t="s">
         <v>30</v>
